--- a/data/nfm_portrait.xlsx
+++ b/data/nfm_portrait.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>seq</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>image_urls</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -516,7 +521,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8577336.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8577334.do</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -527,6 +532,11 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>PS0100200100108140000000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8577334.do; https://www.nfm.go.kr/common/apiimage/relic/8577335.do; https://www.nfm.go.kr/common/apiimage/relic/8577336.do; https://www.nfm.go.kr/common/apiimage/relic/8577337.do; https://www.nfm.go.kr/common/apiimage/relic/8577340.do; https://www.nfm.go.kr/common/apiimage/relic/8577339.do; https://www.nfm.go.kr/common/apiimage/relic/8577341.do; https://www.nfm.go.kr/common/apiimage/relic/8577332.do; https://www.nfm.go.kr/common/apiimage/relic/8577333.do; https://www.nfm.go.kr/common/apiimage/relic/8577338.do</t>
         </is>
       </c>
     </row>
@@ -573,7 +583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8581573.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8581572.do</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -584,6 +594,11 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>PS0100200100109555800000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8581572.do; https://www.nfm.go.kr/common/apiimage/relic/8581562.do; https://www.nfm.go.kr/common/apiimage/relic/8581569.do; https://www.nfm.go.kr/common/apiimage/relic/8581564.do; https://www.nfm.go.kr/common/apiimage/relic/8581570.do; https://www.nfm.go.kr/common/apiimage/relic/8581567.do; https://www.nfm.go.kr/common/apiimage/relic/8581568.do; https://www.nfm.go.kr/common/apiimage/relic/8581571.do; https://www.nfm.go.kr/common/apiimage/relic/8581563.do; https://www.nfm.go.kr/common/apiimage/relic/8581573.do; https://www.nfm.go.kr/common/apiimage/relic/8581565.do; https://www.nfm.go.kr/common/apiimage/relic/8581566.do</t>
         </is>
       </c>
     </row>
@@ -615,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>가로 : 54 세로 : 134</t>
+          <t>세로 : 134 가로 : 54</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -630,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8551073.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8551076.do</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -641,6 +656,11 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>PS0100200100104045500000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8551076.do; https://www.nfm.go.kr/common/apiimage/relic/8551075.do; https://www.nfm.go.kr/common/apiimage/relic/8551074.do; https://www.nfm.go.kr/common/apiimage/relic/8551073.do</t>
         </is>
       </c>
     </row>
@@ -687,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8357057.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357056.do</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -698,6 +718,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>PS0100200100104045600000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357056.do; https://www.nfm.go.kr/common/apiimage/relic/8357055.do; https://www.nfm.go.kr/common/apiimage/relic/8357054.do; https://www.nfm.go.kr/common/apiimage/relic/8357057.do</t>
         </is>
       </c>
     </row>
@@ -729,7 +754,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>가로 : 80.6 세로 : 156.5</t>
+          <t>세로 : 156.5 가로 : 80.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -744,7 +769,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8367916.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8367916.do</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -755,6 +780,11 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>PS0100200100104043800000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8367916.do; https://www.nfm.go.kr/common/apiimage/relic/8367921.do</t>
         </is>
       </c>
     </row>
@@ -801,7 +831,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8537945.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537945.do</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -812,6 +842,11 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>PS0100200100103971700000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537945.do</t>
         </is>
       </c>
     </row>
@@ -843,7 +878,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>가로 : 75 세로 : 160</t>
+          <t>세로 : 160 가로 : 75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -858,7 +893,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8549292.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8549292.do</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -869,6 +904,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>PS0100200100104547900000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8549292.do</t>
         </is>
       </c>
     </row>
@@ -900,7 +940,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>가로 : 72.5 세로 : 116</t>
+          <t>세로 : 116 가로 : 72.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -915,7 +955,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8355326.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8355326.do</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -926,6 +966,11 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>PS0100200100103971600000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8355326.do</t>
         </is>
       </c>
     </row>
@@ -972,7 +1017,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8373940.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8373940.do</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -983,6 +1028,11 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>PS0100200100105782100000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8373940.do</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1064,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>가로 : 90 세로 : 132.3</t>
+          <t>세로 : 132.3 가로 : 90</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1029,7 +1079,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8363190.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8363190.do</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1040,6 +1090,11 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>PS0100200100104716300000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8363190.do</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1126,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>두께 : 0.4 가로 : 21.1 세로 : 15.5</t>
+          <t>세로 : 15.5 가로 : 21.1 두께 : 0.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1086,7 +1141,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8608920.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8608917.do</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1097,6 +1152,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>PS0100200100110348400000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8608917.do; https://www.nfm.go.kr/common/apiimage/relic/8608916.do; https://www.nfm.go.kr/common/apiimage/relic/8608919.do; https://www.nfm.go.kr/common/apiimage/relic/8608918.do; https://www.nfm.go.kr/common/apiimage/relic/8608920.do</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1203,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8607830.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8607829.do</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1154,6 +1214,11 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>PS0100200100110373000000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8607829.do; https://www.nfm.go.kr/common/apiimage/relic/8607830.do</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1245,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>문화예술-서화-회화 / 미디어-아카이브-사진기록</t>
+          <t>미디어-아카이브-사진기록 / 문화예술-서화-회화</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8352005.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8352005.do</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1211,6 +1276,11 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>PS0100200100103754400000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8352005.do</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1312,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>가로 : 88 세로 : 50</t>
+          <t>세로 : 50 가로 : 88</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1257,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8606769.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8606768.do</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1268,6 +1338,11 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>PS0100200100110372600000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8606768.do; https://www.nfm.go.kr/common/apiimage/relic/8606769.do</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8353809.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8353809.do</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1325,6 +1400,11 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>PS0100200100103754500000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8353809.do</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1436,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>세로 : 98.5 가로 : 150</t>
+          <t>가로 : 150 세로 : 98.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1371,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8557482.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8557482.do</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1382,6 +1462,11 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>PS0100200100104547800000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8557482.do</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1498,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>가로 : 67.5 세로 : 113.5</t>
+          <t>세로 : 113.5 가로 : 67.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1428,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8451895.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8451894.do</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1439,6 +1524,11 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>PS0100200100108399800000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8451894.do; https://www.nfm.go.kr/common/apiimage/relic/8451895.do</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1560,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>가로 : 35.5 세로 : 44</t>
+          <t>세로 : 44 가로 : 35.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1485,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8368252.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8368252.do</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1496,6 +1586,11 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>PS0100200100105167600000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8368252.do</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1622,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>세로 : 44 가로 : 35.5</t>
+          <t>가로 : 35.5 세로 : 44</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1542,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8394614.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8394614.do</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1553,6 +1648,11 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>PS0100200100105167700000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8394614.do</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1684,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>세로 : 197 가로 : 60</t>
+          <t>가로 : 60 세로 : 197</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1599,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8605721.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8605721.do</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1610,6 +1710,11 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>PS0100200100110371000000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8605721.do; https://www.nfm.go.kr/common/apiimage/relic/8605722.do</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8605724.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8605724.do</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1667,6 +1772,11 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>PS0100200100110371100000</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8605724.do; https://www.nfm.go.kr/common/apiimage/relic/8605723.do</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1808,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>높이 : 85 가로 : 53.5</t>
+          <t>가로 : 53.5 높이 : 85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1713,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8541958.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8541958.do</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1724,6 +1834,11 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>PS0100200100104045900000</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8541958.do</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8457594.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8457595.do</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1781,6 +1896,11 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>PS0100200100107856200000</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8457595.do; https://www.nfm.go.kr/common/apiimage/relic/8457594.do</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1932,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>가로 : 73 세로 : 109</t>
+          <t>세로 : 109 가로 : 73</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1827,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8463619.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8463619.do</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1838,6 +1958,11 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>PS0100200100108105000000</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8463619.do</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1994,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>세로 : 58 두께 : 2 가로 : 41.5</t>
+          <t>세로 : 58 가로 : 41.5 두께 : 2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1884,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8491292.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491288.do</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1895,6 +2020,11 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>PS0100200100109972500000</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491288.do; https://www.nfm.go.kr/common/apiimage/relic/8491292.do; https://www.nfm.go.kr/common/apiimage/relic/8491291.do; https://www.nfm.go.kr/common/apiimage/relic/8491289.do; https://www.nfm.go.kr/common/apiimage/relic/8491290.do</t>
         </is>
       </c>
     </row>
@@ -1926,7 +2056,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>세로 : 232.5 가로 : 111</t>
+          <t>가로 : 111 세로 : 232.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1941,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8553538.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8553538.do</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1952,6 +2082,11 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>PS0100200100103087500000</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8553538.do</t>
         </is>
       </c>
     </row>
@@ -1983,7 +2118,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>세로 : 32 가로 : 23</t>
+          <t>가로 : 23 세로 : 32</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1998,7 +2133,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8292747.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8292746.do</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2009,6 +2144,11 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>PS0100200100300000100000</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8292746.do; https://www.nfm.go.kr/common/apiimage/relic/8292747.do</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2180,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>세로 : 111.3 가로 : 65</t>
+          <t>가로 : 65 세로 : 111.3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2055,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8548707.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8548708.do</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2066,6 +2206,11 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>PS0100200100104022400000</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8548708.do; https://www.nfm.go.kr/common/apiimage/relic/8548707.do</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2242,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>가로 : 88.5 세로 : 149.5</t>
+          <t>세로 : 149.5 가로 : 88.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2112,7 +2257,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8463194.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8463195.do</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2123,6 +2268,11 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>PS0100200100108104700000</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8463195.do; https://www.nfm.go.kr/common/apiimage/relic/8463194.do</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2304,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>가로 : 95.5 세로 : 136</t>
+          <t>세로 : 136 가로 : 95.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2169,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8591275.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8591275.do</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2180,6 +2330,11 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>PS0100200100107030600000</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8591275.do</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8481121.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8481121.do</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2237,6 +2392,11 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>PS0100200100109335000000</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8481121.do; https://www.nfm.go.kr/common/apiimage/relic/8481122.do</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2428,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>가로 : 67 두께 : 6.7 세로 : 144.5</t>
+          <t>두께 : 6.7 세로 : 144.5 가로 : 67</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2283,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8491285.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491286.do</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2294,6 +2454,11 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>PS0100200100109972300000</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491286.do; https://www.nfm.go.kr/common/apiimage/relic/8491283.do; https://www.nfm.go.kr/common/apiimage/relic/8491281.do; https://www.nfm.go.kr/common/apiimage/relic/8491284.do; https://www.nfm.go.kr/common/apiimage/relic/8491287.do; https://www.nfm.go.kr/common/apiimage/relic/8491282.do; https://www.nfm.go.kr/common/apiimage/relic/8491280.do; https://www.nfm.go.kr/common/apiimage/relic/8491285.do</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8442113.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8442113.do</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2351,6 +2516,11 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>PS0100200100107516900000</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8442113.do</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2567,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8471283.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8471283.do</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2408,6 +2578,11 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>PS0100200100107885400000</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8471283.do; https://www.nfm.go.kr/common/apiimage/relic/8471284.do</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2629,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8524147.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8524148.do</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2465,6 +2640,11 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>PS0100200100103965000000</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8524148.do; https://www.nfm.go.kr/common/apiimage/relic/8524147.do; https://www.nfm.go.kr/common/apiimage/relic/8524146.do</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2691,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8458895.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8458895.do</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2522,6 +2702,11 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>PS0100200100108140100000</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8458895.do; https://www.nfm.go.kr/common/apiimage/relic/8458893.do; https://www.nfm.go.kr/common/apiimage/relic/8458894.do</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2738,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>세로 : 72 가로 : 64</t>
+          <t>가로 : 64 세로 : 72</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2568,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8537907.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537907.do</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2579,6 +2764,11 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>PS0100200100103754300000</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537907.do</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2800,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>가로 : 81.5 세로 : 141</t>
+          <t>세로 : 141 가로 : 81.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2625,7 +2815,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8357692.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357693.do</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2636,6 +2826,11 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>PS0100200100103965400000</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357693.do; https://www.nfm.go.kr/common/apiimage/relic/8357692.do; https://www.nfm.go.kr/common/apiimage/relic/8357694.do</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2862,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>가로 : 36.5 세로 : 45.5</t>
+          <t>세로 : 45.5 가로 : 36.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2682,7 +2877,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8448072.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8448072.do</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2693,6 +2888,11 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>PS0100200100107030700000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8448072.do</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2939,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8561513.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8561513.do</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2750,6 +2950,11 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>PS0100200100104586200000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8561513.do</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2986,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>세로 : 42 가로 : 66.5</t>
+          <t>가로 : 66.5 세로 : 42</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2796,7 +3001,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8389176.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8389174.do</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2807,6 +3012,11 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>PS0100200100101529500000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8389174.do; https://www.nfm.go.kr/common/apiimage/relic/8389176.do; https://www.nfm.go.kr/common/apiimage/relic/8389175.do</t>
         </is>
       </c>
     </row>
@@ -2853,7 +3063,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8240104.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8240104.do</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2864,6 +3074,11 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>PS0100200100106374200000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8240104.do</t>
         </is>
       </c>
     </row>
@@ -2895,7 +3110,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>가로 : 24.2 세로 : 27.3</t>
+          <t>세로 : 27.3 가로 : 24.2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2910,7 +3125,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8461427.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8461428.do</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2921,6 +3136,11 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>PS0100200100107832700000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8461428.do; https://www.nfm.go.kr/common/apiimage/relic/8461427.do</t>
         </is>
       </c>
     </row>
@@ -2967,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8537615.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537619.do</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2978,6 +3198,11 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>PS0100200100103754000000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537619.do; https://www.nfm.go.kr/common/apiimage/relic/8537616.do; https://www.nfm.go.kr/common/apiimage/relic/8537620.do; https://www.nfm.go.kr/common/apiimage/relic/8537615.do; https://www.nfm.go.kr/common/apiimage/relic/8537622.do; https://www.nfm.go.kr/common/apiimage/relic/8537618.do; https://www.nfm.go.kr/common/apiimage/relic/8537621.do; https://www.nfm.go.kr/common/apiimage/relic/8537617.do</t>
         </is>
       </c>
     </row>

--- a/data/nfm_portrait.xlsx
+++ b/data/nfm_portrait.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8577334.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8577332.do</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8577334.do; https://www.nfm.go.kr/common/apiimage/relic/8577335.do; https://www.nfm.go.kr/common/apiimage/relic/8577336.do; https://www.nfm.go.kr/common/apiimage/relic/8577337.do; https://www.nfm.go.kr/common/apiimage/relic/8577340.do; https://www.nfm.go.kr/common/apiimage/relic/8577339.do; https://www.nfm.go.kr/common/apiimage/relic/8577341.do; https://www.nfm.go.kr/common/apiimage/relic/8577332.do; https://www.nfm.go.kr/common/apiimage/relic/8577333.do; https://www.nfm.go.kr/common/apiimage/relic/8577338.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8577332.do; https://www.nfm.go.kr/common/apiimage/relic/8577334.do; https://www.nfm.go.kr/common/apiimage/relic/8577339.do; https://www.nfm.go.kr/common/apiimage/relic/8577336.do; https://www.nfm.go.kr/common/apiimage/relic/8577341.do; https://www.nfm.go.kr/common/apiimage/relic/8577337.do; https://www.nfm.go.kr/common/apiimage/relic/8577340.do; https://www.nfm.go.kr/common/apiimage/relic/8577333.do; https://www.nfm.go.kr/common/apiimage/relic/8577338.do; https://www.nfm.go.kr/common/apiimage/relic/8577335.do</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>가로 : 89.5 세로 : 151.5</t>
+          <t>세로 : 151.5 가로 : 89.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8581572.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8581570.do</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8581572.do; https://www.nfm.go.kr/common/apiimage/relic/8581562.do; https://www.nfm.go.kr/common/apiimage/relic/8581569.do; https://www.nfm.go.kr/common/apiimage/relic/8581564.do; https://www.nfm.go.kr/common/apiimage/relic/8581570.do; https://www.nfm.go.kr/common/apiimage/relic/8581567.do; https://www.nfm.go.kr/common/apiimage/relic/8581568.do; https://www.nfm.go.kr/common/apiimage/relic/8581571.do; https://www.nfm.go.kr/common/apiimage/relic/8581563.do; https://www.nfm.go.kr/common/apiimage/relic/8581573.do; https://www.nfm.go.kr/common/apiimage/relic/8581565.do; https://www.nfm.go.kr/common/apiimage/relic/8581566.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8581570.do; https://www.nfm.go.kr/common/apiimage/relic/8581571.do; https://www.nfm.go.kr/common/apiimage/relic/8581565.do; https://www.nfm.go.kr/common/apiimage/relic/8581564.do; https://www.nfm.go.kr/common/apiimage/relic/8581568.do; https://www.nfm.go.kr/common/apiimage/relic/8581572.do; https://www.nfm.go.kr/common/apiimage/relic/8581566.do; https://www.nfm.go.kr/common/apiimage/relic/8581569.do; https://www.nfm.go.kr/common/apiimage/relic/8581563.do; https://www.nfm.go.kr/common/apiimage/relic/8581567.do; https://www.nfm.go.kr/common/apiimage/relic/8581562.do; https://www.nfm.go.kr/common/apiimage/relic/8581573.do</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>세로 : 134 가로 : 54</t>
+          <t>가로 : 54 세로 : 134</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8551076.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8551075.do</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8551076.do; https://www.nfm.go.kr/common/apiimage/relic/8551075.do; https://www.nfm.go.kr/common/apiimage/relic/8551074.do; https://www.nfm.go.kr/common/apiimage/relic/8551073.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8551075.do; https://www.nfm.go.kr/common/apiimage/relic/8551076.do; https://www.nfm.go.kr/common/apiimage/relic/8551074.do; https://www.nfm.go.kr/common/apiimage/relic/8551073.do</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>세로 : 134 가로 : 54</t>
+          <t>가로 : 54 세로 : 134</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357056.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357057.do</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357056.do; https://www.nfm.go.kr/common/apiimage/relic/8357055.do; https://www.nfm.go.kr/common/apiimage/relic/8357054.do; https://www.nfm.go.kr/common/apiimage/relic/8357057.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357057.do; https://www.nfm.go.kr/common/apiimage/relic/8357054.do; https://www.nfm.go.kr/common/apiimage/relic/8357056.do; https://www.nfm.go.kr/common/apiimage/relic/8357055.do</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8367916.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8367921.do</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8367916.do; https://www.nfm.go.kr/common/apiimage/relic/8367921.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8367921.do; https://www.nfm.go.kr/common/apiimage/relic/8367916.do</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>가로 : 64 세로 : 100</t>
+          <t>세로 : 100 가로 : 64</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>세로 : 160 가로 : 75</t>
+          <t>가로 : 75 세로 : 160</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>가로 : 94.7 세로 : 165.5</t>
+          <t>세로 : 165.5 가로 : 94.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>세로 : 132.3 가로 : 90</t>
+          <t>가로 : 90 세로 : 132.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>세로 : 15.5 가로 : 21.1 두께 : 0.4</t>
+          <t>두께 : 0.4 가로 : 21.1 세로 : 15.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8608917.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8608918.do</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8608917.do; https://www.nfm.go.kr/common/apiimage/relic/8608916.do; https://www.nfm.go.kr/common/apiimage/relic/8608919.do; https://www.nfm.go.kr/common/apiimage/relic/8608918.do; https://www.nfm.go.kr/common/apiimage/relic/8608920.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8608918.do; https://www.nfm.go.kr/common/apiimage/relic/8608916.do; https://www.nfm.go.kr/common/apiimage/relic/8608917.do; https://www.nfm.go.kr/common/apiimage/relic/8608919.do; https://www.nfm.go.kr/common/apiimage/relic/8608920.do</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>가로 : 112.5 세로 : 53.2</t>
+          <t>세로 : 53.2 가로 : 112.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8606768.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8606769.do</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8606768.do; https://www.nfm.go.kr/common/apiimage/relic/8606769.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8606769.do; https://www.nfm.go.kr/common/apiimage/relic/8606768.do</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>세로 : 29.5 가로 : 23.3</t>
+          <t>가로 : 23.3 세로 : 29.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>세로 : 113.5 가로 : 67.5</t>
+          <t>가로 : 67.5 세로 : 113.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>세로 : 44 가로 : 35.5</t>
+          <t>가로 : 35.5 세로 : 44</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>가로 : 53.5 높이 : 85</t>
+          <t>높이 : 85 가로 : 53.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>세로 : 58 가로 : 41.5 두께 : 2</t>
+          <t>세로 : 58 두께 : 2 가로 : 41.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491288.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491291.do</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491288.do; https://www.nfm.go.kr/common/apiimage/relic/8491292.do; https://www.nfm.go.kr/common/apiimage/relic/8491291.do; https://www.nfm.go.kr/common/apiimage/relic/8491289.do; https://www.nfm.go.kr/common/apiimage/relic/8491290.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491291.do; https://www.nfm.go.kr/common/apiimage/relic/8491290.do; https://www.nfm.go.kr/common/apiimage/relic/8491288.do; https://www.nfm.go.kr/common/apiimage/relic/8491289.do; https://www.nfm.go.kr/common/apiimage/relic/8491292.do</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>가로 : 111 세로 : 232.5</t>
+          <t>세로 : 232.5 가로 : 111</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8548708.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8548707.do</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8548708.do; https://www.nfm.go.kr/common/apiimage/relic/8548707.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8548707.do; https://www.nfm.go.kr/common/apiimage/relic/8548708.do</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8463195.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8463194.do</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8463195.do; https://www.nfm.go.kr/common/apiimage/relic/8463194.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8463194.do; https://www.nfm.go.kr/common/apiimage/relic/8463195.do</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>세로 : 136 가로 : 95.5</t>
+          <t>가로 : 95.5 세로 : 136</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8481121.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8481122.do</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8481121.do; https://www.nfm.go.kr/common/apiimage/relic/8481122.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8481122.do; https://www.nfm.go.kr/common/apiimage/relic/8481121.do</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>두께 : 6.7 세로 : 144.5 가로 : 67</t>
+          <t>세로 : 144.5 두께 : 6.7 가로 : 67</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491286.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491282.do</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8491286.do; https://www.nfm.go.kr/common/apiimage/relic/8491283.do; https://www.nfm.go.kr/common/apiimage/relic/8491281.do; https://www.nfm.go.kr/common/apiimage/relic/8491284.do; https://www.nfm.go.kr/common/apiimage/relic/8491287.do; https://www.nfm.go.kr/common/apiimage/relic/8491282.do; https://www.nfm.go.kr/common/apiimage/relic/8491280.do; https://www.nfm.go.kr/common/apiimage/relic/8491285.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8491282.do; https://www.nfm.go.kr/common/apiimage/relic/8491286.do; https://www.nfm.go.kr/common/apiimage/relic/8491280.do; https://www.nfm.go.kr/common/apiimage/relic/8491283.do; https://www.nfm.go.kr/common/apiimage/relic/8491285.do; https://www.nfm.go.kr/common/apiimage/relic/8491284.do; https://www.nfm.go.kr/common/apiimage/relic/8491281.do; https://www.nfm.go.kr/common/apiimage/relic/8491287.do</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8524148.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8524146.do</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8524148.do; https://www.nfm.go.kr/common/apiimage/relic/8524147.do; https://www.nfm.go.kr/common/apiimage/relic/8524146.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8524146.do; https://www.nfm.go.kr/common/apiimage/relic/8524148.do; https://www.nfm.go.kr/common/apiimage/relic/8524147.do</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8458895.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8458893.do</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8458895.do; https://www.nfm.go.kr/common/apiimage/relic/8458893.do; https://www.nfm.go.kr/common/apiimage/relic/8458894.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8458893.do; https://www.nfm.go.kr/common/apiimage/relic/8458895.do; https://www.nfm.go.kr/common/apiimage/relic/8458894.do</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>가로 : 64 세로 : 72</t>
+          <t>세로 : 72 가로 : 64</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357693.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357694.do</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8357693.do; https://www.nfm.go.kr/common/apiimage/relic/8357692.do; https://www.nfm.go.kr/common/apiimage/relic/8357694.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8357694.do; https://www.nfm.go.kr/common/apiimage/relic/8357692.do; https://www.nfm.go.kr/common/apiimage/relic/8357693.do</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>가로 : 58 세로 : 118</t>
+          <t>세로 : 118 가로 : 58</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>세로 : 27.3 가로 : 24.2</t>
+          <t>가로 : 24.2 세로 : 27.3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8461428.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8461427.do</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8461428.do; https://www.nfm.go.kr/common/apiimage/relic/8461427.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8461427.do; https://www.nfm.go.kr/common/apiimage/relic/8461428.do</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>가로 : 73 세로 : 113.5 두께 : 7.5</t>
+          <t>세로 : 113.5 가로 : 73 두께 : 7.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537619.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537617.do</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8537619.do; https://www.nfm.go.kr/common/apiimage/relic/8537616.do; https://www.nfm.go.kr/common/apiimage/relic/8537620.do; https://www.nfm.go.kr/common/apiimage/relic/8537615.do; https://www.nfm.go.kr/common/apiimage/relic/8537622.do; https://www.nfm.go.kr/common/apiimage/relic/8537618.do; https://www.nfm.go.kr/common/apiimage/relic/8537621.do; https://www.nfm.go.kr/common/apiimage/relic/8537617.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8537617.do; https://www.nfm.go.kr/common/apiimage/relic/8537622.do; https://www.nfm.go.kr/common/apiimage/relic/8537618.do; https://www.nfm.go.kr/common/apiimage/relic/8537619.do; https://www.nfm.go.kr/common/apiimage/relic/8537621.do; https://www.nfm.go.kr/common/apiimage/relic/8537620.do; https://www.nfm.go.kr/common/apiimage/relic/8537616.do; https://www.nfm.go.kr/common/apiimage/relic/8537615.do</t>
         </is>
       </c>
     </row>
